--- a/artfynd/A 21372-2025 artfynd.xlsx
+++ b/artfynd/A 21372-2025 artfynd.xlsx
@@ -1063,50 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127403360</v>
+        <v>127407014</v>
       </c>
       <c r="B6" t="n">
-        <v>56849</v>
+        <v>80117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591672</v>
+        <v>591786</v>
       </c>
       <c r="R6" t="n">
-        <v>6984476</v>
+        <v>6984477</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,45 +1160,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127407014</v>
+        <v>127403360</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>56849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591786</v>
+        <v>591672</v>
       </c>
       <c r="R7" t="n">
-        <v>6984477</v>
+        <v>6984476</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 21372-2025 artfynd.xlsx
+++ b/artfynd/A 21372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127407025</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127407041</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127403247</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,45 +966,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127403374</v>
+        <v>127403360</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>56853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591645</v>
+        <v>591672</v>
       </c>
       <c r="R5" t="n">
-        <v>6984489</v>
+        <v>6984476</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127407014</v>
+        <v>127403374</v>
       </c>
       <c r="B6" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591786</v>
+        <v>591645</v>
       </c>
       <c r="R6" t="n">
-        <v>6984477</v>
+        <v>6984489</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,50 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127403360</v>
+        <v>127407014</v>
       </c>
       <c r="B7" t="n">
-        <v>56849</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591672</v>
+        <v>591786</v>
       </c>
       <c r="R7" t="n">
-        <v>6984476</v>
+        <v>6984477</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 21372-2025 artfynd.xlsx
+++ b/artfynd/A 21372-2025 artfynd.xlsx
@@ -966,50 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127403360</v>
+        <v>127403374</v>
       </c>
       <c r="B5" t="n">
-        <v>56853</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591672</v>
+        <v>591645</v>
       </c>
       <c r="R5" t="n">
-        <v>6984476</v>
+        <v>6984489</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127403374</v>
+        <v>127407014</v>
       </c>
       <c r="B6" t="n">
         <v>80121</v>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591645</v>
+        <v>591786</v>
       </c>
       <c r="R6" t="n">
-        <v>6984489</v>
+        <v>6984477</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,45 +1160,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127407014</v>
+        <v>127403360</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>56853</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591786</v>
+        <v>591672</v>
       </c>
       <c r="R7" t="n">
-        <v>6984477</v>
+        <v>6984476</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 21372-2025 artfynd.xlsx
+++ b/artfynd/A 21372-2025 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127403374</v>
+        <v>127407014</v>
       </c>
       <c r="B5" t="n">
         <v>80121</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591645</v>
+        <v>591786</v>
       </c>
       <c r="R5" t="n">
-        <v>6984489</v>
+        <v>6984477</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,45 +1063,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127407014</v>
+        <v>127403360</v>
       </c>
       <c r="B6" t="n">
-        <v>80121</v>
+        <v>56853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591786</v>
+        <v>591672</v>
       </c>
       <c r="R6" t="n">
-        <v>6984477</v>
+        <v>6984476</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,50 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127403360</v>
+        <v>127403374</v>
       </c>
       <c r="B7" t="n">
-        <v>56853</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591672</v>
+        <v>591645</v>
       </c>
       <c r="R7" t="n">
-        <v>6984476</v>
+        <v>6984489</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 21372-2025 artfynd.xlsx
+++ b/artfynd/A 21372-2025 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127407014</v>
+        <v>127403374</v>
       </c>
       <c r="B5" t="n">
         <v>80121</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591786</v>
+        <v>591645</v>
       </c>
       <c r="R5" t="n">
-        <v>6984477</v>
+        <v>6984489</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,50 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127403360</v>
+        <v>127407014</v>
       </c>
       <c r="B6" t="n">
-        <v>56853</v>
+        <v>80121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591672</v>
+        <v>591786</v>
       </c>
       <c r="R6" t="n">
-        <v>6984476</v>
+        <v>6984477</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,45 +1160,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127403374</v>
+        <v>127403360</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>56853</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591645</v>
+        <v>591672</v>
       </c>
       <c r="R7" t="n">
-        <v>6984489</v>
+        <v>6984476</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 21372-2025 artfynd.xlsx
+++ b/artfynd/A 21372-2025 artfynd.xlsx
@@ -966,45 +966,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127403374</v>
+        <v>127403360</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>56853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591645</v>
+        <v>591672</v>
       </c>
       <c r="R5" t="n">
-        <v>6984489</v>
+        <v>6984476</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127407014</v>
+        <v>127403374</v>
       </c>
       <c r="B6" t="n">
         <v>80121</v>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591786</v>
+        <v>591645</v>
       </c>
       <c r="R6" t="n">
-        <v>6984477</v>
+        <v>6984489</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,50 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127403360</v>
+        <v>127407014</v>
       </c>
       <c r="B7" t="n">
-        <v>56853</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591672</v>
+        <v>591786</v>
       </c>
       <c r="R7" t="n">
-        <v>6984476</v>
+        <v>6984477</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 21372-2025 artfynd.xlsx
+++ b/artfynd/A 21372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127407025</v>
       </c>
       <c r="B2" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127407041</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127403247</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,50 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127403360</v>
+        <v>127403374</v>
       </c>
       <c r="B5" t="n">
-        <v>56853</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591672</v>
+        <v>591645</v>
       </c>
       <c r="R5" t="n">
-        <v>6984476</v>
+        <v>6984489</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127403374</v>
+        <v>127407014</v>
       </c>
       <c r="B6" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591645</v>
+        <v>591786</v>
       </c>
       <c r="R6" t="n">
-        <v>6984489</v>
+        <v>6984477</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,45 +1160,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127407014</v>
+        <v>127403360</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>56855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591786</v>
+        <v>591672</v>
       </c>
       <c r="R7" t="n">
-        <v>6984477</v>
+        <v>6984476</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 21372-2025 artfynd.xlsx
+++ b/artfynd/A 21372-2025 artfynd.xlsx
@@ -966,45 +966,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127403374</v>
+        <v>127403360</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>56855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591645</v>
+        <v>591672</v>
       </c>
       <c r="R5" t="n">
-        <v>6984489</v>
+        <v>6984476</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127407014</v>
+        <v>127403374</v>
       </c>
       <c r="B6" t="n">
         <v>80123</v>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591786</v>
+        <v>591645</v>
       </c>
       <c r="R6" t="n">
-        <v>6984477</v>
+        <v>6984489</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,50 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127403360</v>
+        <v>127407014</v>
       </c>
       <c r="B7" t="n">
-        <v>56855</v>
+        <v>80123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591672</v>
+        <v>591786</v>
       </c>
       <c r="R7" t="n">
-        <v>6984476</v>
+        <v>6984477</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 21372-2025 artfynd.xlsx
+++ b/artfynd/A 21372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127407025</v>
       </c>
       <c r="B2" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127407041</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127403247</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,50 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127403360</v>
+        <v>127403374</v>
       </c>
       <c r="B5" t="n">
-        <v>56855</v>
+        <v>80126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591672</v>
+        <v>591645</v>
       </c>
       <c r="R5" t="n">
-        <v>6984476</v>
+        <v>6984489</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127403374</v>
+        <v>127407014</v>
       </c>
       <c r="B6" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591645</v>
+        <v>591786</v>
       </c>
       <c r="R6" t="n">
-        <v>6984489</v>
+        <v>6984477</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,45 +1160,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127407014</v>
+        <v>127403360</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>56858</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591786</v>
+        <v>591672</v>
       </c>
       <c r="R7" t="n">
-        <v>6984477</v>
+        <v>6984476</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 21372-2025 artfynd.xlsx
+++ b/artfynd/A 21372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127407025</v>
       </c>
       <c r="B2" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127407041</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127403247</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,45 +966,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127403374</v>
+        <v>127403360</v>
       </c>
       <c r="B5" t="n">
-        <v>80126</v>
+        <v>56864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591645</v>
+        <v>591672</v>
       </c>
       <c r="R5" t="n">
-        <v>6984489</v>
+        <v>6984476</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127407014</v>
+        <v>127403374</v>
       </c>
       <c r="B6" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591786</v>
+        <v>591645</v>
       </c>
       <c r="R6" t="n">
-        <v>6984477</v>
+        <v>6984489</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,50 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127403360</v>
+        <v>127407014</v>
       </c>
       <c r="B7" t="n">
-        <v>56858</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591672</v>
+        <v>591786</v>
       </c>
       <c r="R7" t="n">
-        <v>6984476</v>
+        <v>6984477</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 21372-2025 artfynd.xlsx
+++ b/artfynd/A 21372-2025 artfynd.xlsx
@@ -966,50 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127403360</v>
+        <v>127403374</v>
       </c>
       <c r="B5" t="n">
-        <v>56864</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591672</v>
+        <v>591645</v>
       </c>
       <c r="R5" t="n">
-        <v>6984476</v>
+        <v>6984489</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127403374</v>
+        <v>127407014</v>
       </c>
       <c r="B6" t="n">
         <v>80132</v>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591645</v>
+        <v>591786</v>
       </c>
       <c r="R6" t="n">
-        <v>6984489</v>
+        <v>6984477</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,45 +1160,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127407014</v>
+        <v>127403360</v>
       </c>
       <c r="B7" t="n">
-        <v>80132</v>
+        <v>56864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591786</v>
+        <v>591672</v>
       </c>
       <c r="R7" t="n">
-        <v>6984477</v>
+        <v>6984476</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 21372-2025 artfynd.xlsx
+++ b/artfynd/A 21372-2025 artfynd.xlsx
@@ -966,45 +966,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127403374</v>
+        <v>127403360</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>56864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591645</v>
+        <v>591672</v>
       </c>
       <c r="R5" t="n">
-        <v>6984489</v>
+        <v>6984476</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127407014</v>
+        <v>127403374</v>
       </c>
       <c r="B6" t="n">
         <v>80132</v>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591786</v>
+        <v>591645</v>
       </c>
       <c r="R6" t="n">
-        <v>6984477</v>
+        <v>6984489</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,50 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127403360</v>
+        <v>127407014</v>
       </c>
       <c r="B7" t="n">
-        <v>56864</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591672</v>
+        <v>591786</v>
       </c>
       <c r="R7" t="n">
-        <v>6984476</v>
+        <v>6984477</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 21372-2025 artfynd.xlsx
+++ b/artfynd/A 21372-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127407025</v>
+        <v>127403247</v>
       </c>
       <c r="B2" t="n">
-        <v>80161</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591786</v>
+        <v>591651</v>
       </c>
       <c r="R2" t="n">
-        <v>6984477</v>
+        <v>6984402</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -775,11 +775,11 @@
         <v>127407041</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127403247</v>
+        <v>127403374</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591651</v>
+        <v>591645</v>
       </c>
       <c r="R4" t="n">
-        <v>6984402</v>
+        <v>6984489</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127403374</v>
+        <v>127407014</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591645</v>
+        <v>591786</v>
       </c>
       <c r="R5" t="n">
-        <v>6984489</v>
+        <v>6984477</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127407014</v>
+        <v>127407025</v>
       </c>
       <c r="B6" t="n">
-        <v>80132</v>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>127403360</v>
       </c>
       <c r="B7" t="n">
-        <v>56864</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 21372-2025 artfynd.xlsx
+++ b/artfynd/A 21372-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127403247</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127407041</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127403374</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127407014</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127407025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,8 +1289,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127403360</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>